--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3A58CA-E477-46D0-9400-F14ADE2E0EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB468D0F-3DEF-43AA-9F74-398D2D2A5E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -34,17 +34,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>employeeId</t>
+  </si>
+  <si>
+    <t>EMP3</t>
+  </si>
+  <si>
+    <t>EMP4</t>
+  </si>
+  <si>
+    <t>EMP0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -72,8 +89,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,13 +411,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11AE4FD-BB0F-42AE-AA99-EC22A381E96E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB468D0F-3DEF-43AA-9F74-398D2D2A5E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8C4904-B219-4099-A98E-2509D177414A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -34,18 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>employeeId</t>
   </si>
   <si>
-    <t>EMP3</t>
-  </si>
-  <si>
-    <t>EMP4</t>
-  </si>
-  <si>
-    <t>EMP0</t>
+    <t>EMP1</t>
   </si>
 </sst>
 </file>
@@ -424,24 +418,20 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8C4904-B219-4099-A98E-2509D177414A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF7A80-7473-497F-ACA6-ADB7E5E1DC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>employeeId</t>
   </si>
   <si>
     <t>EMP1</t>
+  </si>
+  <si>
+    <t>EMP2</t>
   </si>
 </sst>
 </file>
@@ -83,13 +86,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -407,9 +413,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11AE4FD-BB0F-42AE-AA99-EC22A381E96E}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -425,7 +434,9 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF7A80-7473-497F-ACA6-ADB7E5E1DC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F3CD52-C7E4-447E-A484-3815982C6F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -34,15 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>employeeId</t>
   </si>
   <si>
     <t>EMP1</t>
-  </si>
-  <si>
-    <t>EMP2</t>
   </si>
 </sst>
 </file>
@@ -434,9 +431,7 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F3CD52-C7E4-447E-A484-3815982C6F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDDBCB0-ADB0-45B9-9632-C559C8FA6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -34,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>employeeId</t>
-  </si>
-  <si>
-    <t>EMP1</t>
   </si>
 </sst>
 </file>
@@ -423,9 +420,7 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDDBCB0-ADB0-45B9-9632-C559C8FA6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D444088-6B16-4EFB-9DED-E79B074E9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -34,9 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>employeeId</t>
+  </si>
+  <si>
+    <t>EMP1</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,9 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D444088-6B16-4EFB-9DED-E79B074E9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A6DA10-C578-44EF-B50E-7F38674F45FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>employeeId</t>
   </si>
   <si>
     <t>EMP1</t>
+  </si>
+  <si>
+    <t>EMP2</t>
+  </si>
+  <si>
+    <t>EMP4</t>
+  </si>
+  <si>
+    <t>EMP6</t>
+  </si>
+  <si>
+    <t>EMP3</t>
   </si>
 </sst>
 </file>
@@ -408,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11AE4FD-BB0F-42AE-AA99-EC22A381E96E}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
@@ -431,21 +443,33 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A6DA10-C578-44EF-B50E-7F38674F45FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D712762-EA43-4D25-87FF-8C42AEA2D7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -48,10 +48,10 @@
     <t>EMP4</t>
   </si>
   <si>
-    <t>EMP6</t>
-  </si>
-  <si>
     <t>EMP3</t>
+  </si>
+  <si>
+    <t>EMP7</t>
   </si>
 </sst>
 </file>
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11AE4FD-BB0F-42AE-AA99-EC22A381E96E}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
@@ -459,15 +459,17 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Employee-Management-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D712762-EA43-4D25-87FF-8C42AEA2D7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FA8A77-61CA-4753-93E4-4520FB53491C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{20FE3455-6FED-421F-B6D9-E3B6163278E8}"/>
   </bookViews>
@@ -45,13 +45,13 @@
     <t>EMP2</t>
   </si>
   <si>
-    <t>EMP4</t>
-  </si>
-  <si>
-    <t>EMP3</t>
-  </si>
-  <si>
     <t>EMP7</t>
+  </si>
+  <si>
+    <t>EMP6</t>
+  </si>
+  <si>
+    <t>EMP9</t>
   </si>
 </sst>
 </file>
@@ -452,26 +452,27 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
